--- a/윈윈대진_입결.xlsx
+++ b/윈윈대진_입결.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\대진대_입학상담_2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06B5F09C-C981-4021-A6C2-77357B5771C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09687E2C-DB56-49B3-95D4-AAFBCA7D1F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{333CE5E8-D45C-448F-B07C-A850148192AA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{333CE5E8-D45C-448F-B07C-A850148192AA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -905,6 +905,15 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -919,15 +928,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1267,27 +1267,29 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="3.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="13" width="7.875" customWidth="1"/>
+    <col min="2" max="2" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.125" customWidth="1"/>
+    <col min="4" max="13" width="7.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="13" t="s">
@@ -1299,36 +1301,36 @@
       <c r="C2" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="27" t="s">
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="28" t="s">
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="29" t="s">
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="S2" s="31" t="s">
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="S2" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="T2" s="32" t="s">
+      <c r="T2" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="U2" s="32" t="s">
+      <c r="U2" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="V2" s="32" t="s">
+      <c r="V2" s="27" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1372,10 +1374,10 @@
       <c r="O3" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="S3" s="31"/>
-      <c r="T3" s="32"/>
-      <c r="U3" s="32"/>
-      <c r="V3" s="32"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
     </row>
     <row r="4" spans="1:22" ht="22.5">
       <c r="A4" s="20">
@@ -1423,188 +1425,188 @@
       <c r="O4" s="8">
         <v>2.9</v>
       </c>
-      <c r="S4" s="30" t="s">
+      <c r="S4" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="T4" s="30" t="s">
+      <c r="T4" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="U4" s="30">
+      <c r="U4" s="25">
         <v>0</v>
       </c>
-      <c r="V4" s="30">
+      <c r="V4" s="25">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="33.75">
+    <row r="5" spans="1:22">
       <c r="A5" s="22">
         <v>2</v>
       </c>
       <c r="B5" s="9"/>
-      <c r="C5" s="10" t="s">
-        <v>1</v>
+      <c r="C5" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>5.45</v>
+        <v>5.17</v>
       </c>
       <c r="E5" s="3">
-        <v>4.92</v>
+        <v>4.67</v>
       </c>
       <c r="F5" s="2">
-        <v>4.3499999999999996</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="G5" s="4">
-        <v>5.04</v>
+        <v>5.37</v>
       </c>
       <c r="H5" s="5">
-        <v>4.68</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="I5" s="4">
-        <v>4.25</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="J5" s="6">
-        <v>5.75</v>
+        <v>5.84</v>
       </c>
       <c r="K5" s="7">
-        <v>5.24</v>
+        <v>5.23</v>
       </c>
       <c r="L5" s="6">
-        <v>4.47</v>
-      </c>
-      <c r="M5" s="11">
-        <v>4.8</v>
-      </c>
-      <c r="N5" s="11">
-        <v>6.2</v>
-      </c>
-      <c r="O5" s="11">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="S5" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="T5" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="U5" s="30">
-        <v>14</v>
-      </c>
-      <c r="V5" s="30">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="33.75">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="M5" s="8">
+        <v>8.3800000000000008</v>
+      </c>
+      <c r="N5" s="8">
+        <v>9.5</v>
+      </c>
+      <c r="O5" s="8">
+        <v>5.9</v>
+      </c>
+      <c r="S5" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="T5" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="U5" s="25">
+        <v>7</v>
+      </c>
+      <c r="V5" s="25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="20">
         <v>3</v>
       </c>
       <c r="B6" s="12"/>
-      <c r="C6" s="1" t="s">
-        <v>2</v>
+      <c r="C6" s="10" t="s">
+        <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>5.17</v>
+        <v>5.45</v>
       </c>
       <c r="E6" s="3">
-        <v>4.67</v>
+        <v>4.92</v>
       </c>
       <c r="F6" s="2">
-        <v>4.0599999999999996</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="G6" s="4">
-        <v>5.37</v>
+        <v>5.04</v>
       </c>
       <c r="H6" s="5">
-        <v>4.9800000000000004</v>
+        <v>4.68</v>
       </c>
       <c r="I6" s="4">
-        <v>4.0999999999999996</v>
+        <v>4.25</v>
       </c>
       <c r="J6" s="6">
-        <v>5.84</v>
+        <v>5.75</v>
       </c>
       <c r="K6" s="7">
-        <v>5.23</v>
+        <v>5.24</v>
       </c>
       <c r="L6" s="6">
-        <v>4.4800000000000004</v>
-      </c>
-      <c r="M6" s="8">
-        <v>8.3800000000000008</v>
-      </c>
-      <c r="N6" s="8">
-        <v>9.5</v>
-      </c>
-      <c r="O6" s="8">
-        <v>5.9</v>
-      </c>
-      <c r="S6" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="T6" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="U6" s="30">
-        <v>7</v>
-      </c>
-      <c r="V6" s="30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="22.5">
+        <v>4.47</v>
+      </c>
+      <c r="M6" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="N6" s="11">
+        <v>6.2</v>
+      </c>
+      <c r="O6" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="S6" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="T6" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="U6" s="25">
+        <v>14</v>
+      </c>
+      <c r="V6" s="25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" s="22">
         <v>4</v>
       </c>
       <c r="B7" s="9"/>
-      <c r="C7" s="10" t="s">
-        <v>3</v>
+      <c r="C7" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="D7" s="2">
-        <v>5.41</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E7" s="3">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="F7" s="2">
+        <v>3.73</v>
+      </c>
+      <c r="G7" s="4">
         <v>4.8600000000000003</v>
       </c>
-      <c r="F7" s="2">
-        <v>3.57</v>
-      </c>
-      <c r="G7" s="4">
-        <v>5.58</v>
-      </c>
       <c r="H7" s="5">
-        <v>5.29</v>
+        <v>4.57</v>
       </c>
       <c r="I7" s="4">
-        <v>4.62</v>
+        <v>3.98</v>
       </c>
       <c r="J7" s="6">
-        <v>5.85</v>
+        <v>5.47</v>
       </c>
       <c r="K7" s="7">
-        <v>5.41</v>
+        <v>5</v>
       </c>
       <c r="L7" s="6">
-        <v>4.55</v>
-      </c>
-      <c r="M7" s="11">
-        <v>4.7</v>
-      </c>
-      <c r="N7" s="11">
-        <v>4.25</v>
-      </c>
-      <c r="O7" s="11">
-        <v>3.67</v>
-      </c>
-      <c r="S7" s="30" t="s">
+        <v>4.47</v>
+      </c>
+      <c r="M7" s="8">
+        <v>5.5</v>
+      </c>
+      <c r="N7" s="8">
+        <v>7.83</v>
+      </c>
+      <c r="O7" s="8">
+        <v>6.73</v>
+      </c>
+      <c r="S7" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="T7" s="30" t="s">
+      <c r="T7" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="U7" s="30">
-        <v>10</v>
-      </c>
-      <c r="V7" s="30">
-        <v>19</v>
+      <c r="U7" s="25">
+        <v>5</v>
+      </c>
+      <c r="V7" s="25">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1612,56 +1614,56 @@
         <v>5</v>
       </c>
       <c r="B8" s="12"/>
-      <c r="C8" s="1" t="s">
-        <v>4</v>
+      <c r="C8" s="10" t="s">
+        <v>3</v>
       </c>
       <c r="D8" s="2">
-        <v>4.9000000000000004</v>
+        <v>5.41</v>
       </c>
       <c r="E8" s="3">
-        <v>4.4800000000000004</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="F8" s="2">
-        <v>3.73</v>
+        <v>3.57</v>
       </c>
       <c r="G8" s="4">
-        <v>4.8600000000000003</v>
+        <v>5.58</v>
       </c>
       <c r="H8" s="5">
-        <v>4.57</v>
+        <v>5.29</v>
       </c>
       <c r="I8" s="4">
-        <v>3.98</v>
+        <v>4.62</v>
       </c>
       <c r="J8" s="6">
-        <v>5.47</v>
+        <v>5.85</v>
       </c>
       <c r="K8" s="7">
-        <v>5</v>
+        <v>5.41</v>
       </c>
       <c r="L8" s="6">
-        <v>4.47</v>
-      </c>
-      <c r="M8" s="8">
-        <v>5.5</v>
-      </c>
-      <c r="N8" s="8">
-        <v>7.83</v>
-      </c>
-      <c r="O8" s="8">
-        <v>6.73</v>
-      </c>
-      <c r="S8" s="30" t="s">
+        <v>4.55</v>
+      </c>
+      <c r="M8" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="N8" s="11">
+        <v>4.25</v>
+      </c>
+      <c r="O8" s="11">
+        <v>3.67</v>
+      </c>
+      <c r="S8" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="T8" s="30" t="s">
+      <c r="T8" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="U8" s="30">
-        <v>5</v>
-      </c>
-      <c r="V8" s="30">
-        <v>4</v>
+      <c r="U8" s="25">
+        <v>10</v>
+      </c>
+      <c r="V8" s="25">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="22.5">
@@ -1708,74 +1710,74 @@
       <c r="O9" s="11">
         <v>6</v>
       </c>
-      <c r="S9" s="30" t="s">
+      <c r="S9" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="T9" s="30" t="s">
+      <c r="T9" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="U9" s="30">
+      <c r="U9" s="25">
         <v>1</v>
       </c>
-      <c r="V9" s="30">
+      <c r="V9" s="25">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="22.5">
+    <row r="10" spans="1:22">
       <c r="A10" s="20">
         <v>7</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2">
-        <v>5.61</v>
+        <v>5.52</v>
       </c>
       <c r="E10" s="3">
-        <v>5.15</v>
+        <v>5.25</v>
       </c>
       <c r="F10" s="2">
-        <v>4.67</v>
+        <v>4.78</v>
       </c>
       <c r="G10" s="4">
-        <v>5.46</v>
+        <v>5.71</v>
       </c>
       <c r="H10" s="5">
-        <v>4.83</v>
+        <v>5.21</v>
       </c>
       <c r="I10" s="4">
-        <v>3.13</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="J10" s="6">
-        <v>5.76</v>
+        <v>5.45</v>
       </c>
       <c r="K10" s="7">
-        <v>5.24</v>
+        <v>5.19</v>
       </c>
       <c r="L10" s="6">
-        <v>4.5199999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="M10" s="8">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N10" s="8">
+        <v>3.17</v>
+      </c>
+      <c r="O10" s="8">
         <v>3.5</v>
       </c>
-      <c r="O10" s="8">
-        <v>3.7</v>
-      </c>
-      <c r="S10" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="T10" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="U10" s="30">
-        <v>11</v>
-      </c>
-      <c r="V10" s="30">
-        <v>8</v>
+      <c r="S10" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="T10" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="U10" s="25">
+        <v>5</v>
+      </c>
+      <c r="V10" s="25">
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1783,170 +1785,170 @@
         <v>8</v>
       </c>
       <c r="B11" s="9"/>
-      <c r="C11" s="10" t="s">
-        <v>7</v>
+      <c r="C11" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="D11" s="2">
-        <v>6.7</v>
+        <v>5.61</v>
       </c>
       <c r="E11" s="3">
-        <v>6.05</v>
+        <v>5.15</v>
       </c>
       <c r="F11" s="2">
-        <v>4.99</v>
+        <v>4.67</v>
       </c>
       <c r="G11" s="4">
-        <v>6.25</v>
+        <v>5.46</v>
       </c>
       <c r="H11" s="5">
-        <v>5.51</v>
+        <v>4.83</v>
       </c>
       <c r="I11" s="4">
-        <v>4.7699999999999996</v>
+        <v>3.13</v>
       </c>
       <c r="J11" s="6">
-        <v>6.57</v>
+        <v>5.76</v>
       </c>
       <c r="K11" s="7">
-        <v>5.57</v>
+        <v>5.24</v>
       </c>
       <c r="L11" s="6">
-        <v>3.98</v>
-      </c>
-      <c r="M11" s="11">
-        <v>3.33</v>
-      </c>
-      <c r="N11" s="11">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="M11" s="8">
         <v>3.7</v>
       </c>
-      <c r="O11" s="11">
-        <v>3.25</v>
-      </c>
-      <c r="S11" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="T11" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="U11" s="30">
-        <v>2</v>
-      </c>
-      <c r="V11" s="30">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="22.5">
+      <c r="N11" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="O11" s="8">
+        <v>3.7</v>
+      </c>
+      <c r="S11" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="T11" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="U11" s="25">
+        <v>11</v>
+      </c>
+      <c r="V11" s="25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" s="20">
         <v>9</v>
       </c>
       <c r="B12" s="12"/>
-      <c r="C12" s="1" t="s">
-        <v>8</v>
+      <c r="C12" s="10" t="s">
+        <v>7</v>
       </c>
       <c r="D12" s="2">
-        <v>5.52</v>
+        <v>6.7</v>
       </c>
       <c r="E12" s="3">
-        <v>5.25</v>
+        <v>6.05</v>
       </c>
       <c r="F12" s="2">
-        <v>4.78</v>
+        <v>4.99</v>
       </c>
       <c r="G12" s="4">
-        <v>5.71</v>
+        <v>6.25</v>
       </c>
       <c r="H12" s="5">
-        <v>5.21</v>
+        <v>5.51</v>
       </c>
       <c r="I12" s="4">
-        <v>4.6500000000000004</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="J12" s="6">
-        <v>5.45</v>
+        <v>6.57</v>
       </c>
       <c r="K12" s="7">
-        <v>5.19</v>
+        <v>5.57</v>
       </c>
       <c r="L12" s="6">
-        <v>4.3</v>
-      </c>
-      <c r="M12" s="8">
-        <v>3.6</v>
-      </c>
-      <c r="N12" s="8">
-        <v>3.17</v>
-      </c>
-      <c r="O12" s="8">
-        <v>3.5</v>
-      </c>
-      <c r="S12" s="30" t="s">
+        <v>3.98</v>
+      </c>
+      <c r="M12" s="11">
+        <v>3.33</v>
+      </c>
+      <c r="N12" s="11">
+        <v>3.7</v>
+      </c>
+      <c r="O12" s="11">
+        <v>3.25</v>
+      </c>
+      <c r="S12" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="T12" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="U12" s="30">
-        <v>5</v>
-      </c>
-      <c r="V12" s="30">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="22.5">
+      <c r="T12" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="U12" s="25">
+        <v>2</v>
+      </c>
+      <c r="V12" s="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="22">
         <v>10</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D13" s="2">
-        <v>5.76</v>
+        <v>5.75</v>
       </c>
       <c r="E13" s="3">
-        <v>5.22</v>
+        <v>5.55</v>
       </c>
       <c r="F13" s="2">
-        <v>4.5999999999999996</v>
+        <v>5.37</v>
       </c>
       <c r="G13" s="4">
-        <v>5.92</v>
+        <v>5.58</v>
       </c>
       <c r="H13" s="5">
-        <v>5.34</v>
+        <v>5.12</v>
       </c>
       <c r="I13" s="4">
-        <v>4.58</v>
+        <v>4.76</v>
       </c>
       <c r="J13" s="6">
-        <v>5.84</v>
+        <v>5.55</v>
       </c>
       <c r="K13" s="7">
-        <v>5.39</v>
+        <v>4.79</v>
       </c>
       <c r="L13" s="6">
-        <v>4.82</v>
+        <v>3.74</v>
       </c>
       <c r="M13" s="11">
+        <v>5</v>
+      </c>
+      <c r="N13" s="11">
+        <v>5.38</v>
+      </c>
+      <c r="O13" s="11">
+        <v>7.25</v>
+      </c>
+      <c r="S13" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="T13" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="U13" s="25">
+        <v>15</v>
+      </c>
+      <c r="V13" s="25">
         <v>4</v>
-      </c>
-      <c r="N13" s="11">
-        <v>3.75</v>
-      </c>
-      <c r="O13" s="11">
-        <v>3.5</v>
-      </c>
-      <c r="S13" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="T13" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="U13" s="30">
-        <v>12</v>
-      </c>
-      <c r="V13" s="30">
-        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="22.5">
@@ -1993,16 +1995,16 @@
       <c r="O14" s="8">
         <v>10.7</v>
       </c>
-      <c r="S14" s="30" t="s">
+      <c r="S14" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="T14" s="30" t="s">
+      <c r="T14" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="U14" s="30">
+      <c r="U14" s="25">
         <v>13</v>
       </c>
-      <c r="V14" s="30">
+      <c r="V14" s="25">
         <v>19</v>
       </c>
     </row>
@@ -2011,113 +2013,113 @@
         <v>12</v>
       </c>
       <c r="B15" s="9"/>
-      <c r="C15" s="10" t="s">
-        <v>11</v>
+      <c r="C15" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="D15" s="2">
-        <v>5.75</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="E15" s="3">
-        <v>5.55</v>
+        <v>4.51</v>
       </c>
       <c r="F15" s="2">
-        <v>5.37</v>
+        <v>3.97</v>
       </c>
       <c r="G15" s="4">
-        <v>5.58</v>
+        <v>4.88</v>
       </c>
       <c r="H15" s="5">
-        <v>5.12</v>
+        <v>4.51</v>
       </c>
       <c r="I15" s="4">
-        <v>4.76</v>
+        <v>3.16</v>
       </c>
       <c r="J15" s="6">
-        <v>5.55</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="K15" s="7">
-        <v>4.79</v>
+        <v>4.5199999999999996</v>
       </c>
       <c r="L15" s="6">
-        <v>3.74</v>
-      </c>
-      <c r="M15" s="11">
-        <v>5</v>
-      </c>
-      <c r="N15" s="11">
-        <v>5.38</v>
-      </c>
-      <c r="O15" s="11">
-        <v>7.25</v>
-      </c>
-      <c r="S15" s="30" t="s">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="M15" s="8">
+        <v>7.67</v>
+      </c>
+      <c r="N15" s="8">
+        <v>8</v>
+      </c>
+      <c r="O15" s="8">
+        <v>8.83</v>
+      </c>
+      <c r="S15" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="T15" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="U15" s="30">
-        <v>15</v>
-      </c>
-      <c r="V15" s="30">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="33.75">
+      <c r="T15" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="U15" s="25">
+        <v>14</v>
+      </c>
+      <c r="V15" s="25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" s="20">
         <v>13</v>
       </c>
       <c r="B16" s="12"/>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="2">
+        <v>5.76</v>
+      </c>
+      <c r="E16" s="3">
+        <v>5.22</v>
+      </c>
+      <c r="F16" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="G16" s="4">
+        <v>5.92</v>
+      </c>
+      <c r="H16" s="5">
+        <v>5.34</v>
+      </c>
+      <c r="I16" s="4">
+        <v>4.58</v>
+      </c>
+      <c r="J16" s="6">
+        <v>5.84</v>
+      </c>
+      <c r="K16" s="7">
+        <v>5.39</v>
+      </c>
+      <c r="L16" s="6">
+        <v>4.82</v>
+      </c>
+      <c r="M16" s="11">
+        <v>4</v>
+      </c>
+      <c r="N16" s="11">
+        <v>3.75</v>
+      </c>
+      <c r="O16" s="11">
+        <v>3.5</v>
+      </c>
+      <c r="S16" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="T16" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="U16" s="25">
         <v>12</v>
       </c>
-      <c r="D16" s="2">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="E16" s="3">
-        <v>4.51</v>
-      </c>
-      <c r="F16" s="2">
-        <v>3.97</v>
-      </c>
-      <c r="G16" s="4">
-        <v>4.88</v>
-      </c>
-      <c r="H16" s="5">
-        <v>4.51</v>
-      </c>
-      <c r="I16" s="4">
-        <v>3.16</v>
-      </c>
-      <c r="J16" s="6">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="K16" s="7">
-        <v>4.5199999999999996</v>
-      </c>
-      <c r="L16" s="6">
-        <v>4.0599999999999996</v>
-      </c>
-      <c r="M16" s="8">
-        <v>7.67</v>
-      </c>
-      <c r="N16" s="8">
-        <v>8</v>
-      </c>
-      <c r="O16" s="8">
-        <v>8.83</v>
-      </c>
-      <c r="S16" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="T16" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="U16" s="30">
-        <v>14</v>
-      </c>
-      <c r="V16" s="30">
-        <v>14</v>
+      <c r="V16" s="25">
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="22.5">
@@ -2164,16 +2166,16 @@
       <c r="O17" s="11">
         <v>6</v>
       </c>
-      <c r="S17" s="30" t="s">
+      <c r="S17" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="T17" s="30" t="s">
+      <c r="T17" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="U17" s="30">
+      <c r="U17" s="25">
         <v>7</v>
       </c>
-      <c r="V17" s="30">
+      <c r="V17" s="25">
         <v>10</v>
       </c>
     </row>
@@ -2223,16 +2225,16 @@
       <c r="O18" s="8">
         <v>3.8</v>
       </c>
-      <c r="S18" s="30" t="s">
+      <c r="S18" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="T18" s="30" t="s">
+      <c r="T18" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="U18" s="30">
+      <c r="U18" s="25">
         <v>20</v>
       </c>
-      <c r="V18" s="30">
+      <c r="V18" s="25">
         <v>3</v>
       </c>
     </row>
@@ -2241,116 +2243,116 @@
         <v>16</v>
       </c>
       <c r="B19" s="9"/>
-      <c r="C19" s="10" t="s">
-        <v>15</v>
+      <c r="C19" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="D19" s="2">
-        <v>3.96</v>
+        <v>5.28</v>
       </c>
       <c r="E19" s="3">
-        <v>3.6</v>
+        <v>4.62</v>
       </c>
       <c r="F19" s="2">
-        <v>2.75</v>
+        <v>3.14</v>
       </c>
       <c r="G19" s="4">
-        <v>3.83</v>
+        <v>5.33</v>
       </c>
       <c r="H19" s="5">
-        <v>3.53</v>
+        <v>4.78</v>
       </c>
       <c r="I19" s="4">
-        <v>2.7</v>
+        <v>3.56</v>
       </c>
       <c r="J19" s="6">
-        <v>3.76</v>
+        <v>5.17</v>
       </c>
       <c r="K19" s="7">
-        <v>3.42</v>
+        <v>4.51</v>
       </c>
       <c r="L19" s="6">
-        <v>2.66</v>
-      </c>
-      <c r="M19" s="11">
-        <v>6.72</v>
-      </c>
-      <c r="N19" s="11">
-        <v>7.17</v>
-      </c>
-      <c r="O19" s="11">
-        <v>7.75</v>
-      </c>
-      <c r="S19" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="T19" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="U19" s="30">
-        <v>8</v>
-      </c>
-      <c r="V19" s="30">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" ht="22.5">
+        <v>2.98</v>
+      </c>
+      <c r="M19" s="8">
+        <v>5.75</v>
+      </c>
+      <c r="N19" s="8">
+        <v>5.4</v>
+      </c>
+      <c r="O19" s="8">
+        <v>8.9</v>
+      </c>
+      <c r="S19" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="T19" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="U19" s="25">
+        <v>14</v>
+      </c>
+      <c r="V19" s="25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="20">
         <v>17</v>
       </c>
       <c r="B20" s="12"/>
-      <c r="C20" s="1" t="s">
-        <v>16</v>
+      <c r="C20" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="D20" s="2">
-        <v>5.28</v>
+        <v>3.96</v>
       </c>
       <c r="E20" s="3">
-        <v>4.62</v>
+        <v>3.6</v>
       </c>
       <c r="F20" s="2">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="G20" s="4">
-        <v>5.33</v>
+        <v>3.83</v>
       </c>
       <c r="H20" s="5">
-        <v>4.78</v>
+        <v>3.53</v>
       </c>
       <c r="I20" s="4">
-        <v>3.56</v>
+        <v>2.7</v>
       </c>
       <c r="J20" s="6">
-        <v>5.17</v>
+        <v>3.76</v>
       </c>
       <c r="K20" s="7">
-        <v>4.51</v>
+        <v>3.42</v>
       </c>
       <c r="L20" s="6">
-        <v>2.98</v>
-      </c>
-      <c r="M20" s="8">
-        <v>5.75</v>
-      </c>
-      <c r="N20" s="8">
-        <v>5.4</v>
-      </c>
-      <c r="O20" s="8">
-        <v>8.9</v>
-      </c>
-      <c r="S20" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="T20" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="U20" s="30">
-        <v>14</v>
-      </c>
-      <c r="V20" s="30">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" ht="22.5">
+        <v>2.66</v>
+      </c>
+      <c r="M20" s="11">
+        <v>6.72</v>
+      </c>
+      <c r="N20" s="11">
+        <v>7.17</v>
+      </c>
+      <c r="O20" s="11">
+        <v>7.75</v>
+      </c>
+      <c r="S20" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="T20" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="U20" s="25">
+        <v>8</v>
+      </c>
+      <c r="V20" s="25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="22">
         <v>18</v>
       </c>
@@ -2394,20 +2396,20 @@
       <c r="O21" s="11">
         <v>6.13</v>
       </c>
-      <c r="S21" s="30" t="s">
+      <c r="S21" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="T21" s="30" t="s">
+      <c r="T21" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="U21" s="30">
+      <c r="U21" s="25">
         <v>11</v>
       </c>
-      <c r="V21" s="30">
+      <c r="V21" s="25">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="33.75">
+    <row r="22" spans="1:22">
       <c r="A22" s="20">
         <v>19</v>
       </c>
@@ -2415,734 +2417,734 @@
         <v>48</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="2">
-        <v>6.61</v>
-      </c>
-      <c r="E22" s="3">
-        <v>6.15</v>
-      </c>
-      <c r="F22" s="2">
-        <v>5.28</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="2"/>
       <c r="G22" s="4">
-        <v>6.75</v>
+        <v>6.52</v>
       </c>
       <c r="H22" s="5">
-        <v>6.03</v>
+        <v>5.71</v>
       </c>
       <c r="I22" s="4">
-        <v>4.28</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="J22" s="6">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="K22" s="7">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="L22" s="6">
-        <v>4.7</v>
-      </c>
-      <c r="M22" s="8">
-        <v>4.75</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M22" s="8"/>
       <c r="N22" s="8">
-        <v>3.5</v>
+        <v>3.73</v>
       </c>
       <c r="O22" s="8">
-        <v>3.75</v>
-      </c>
-      <c r="S22" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="T22" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="U22" s="30">
-        <v>8</v>
-      </c>
-      <c r="V22" s="30">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" ht="22.5">
+      <c r="S22" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="T22" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="U22" s="25">
+        <v>10</v>
+      </c>
+      <c r="V22" s="25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="22">
         <v>20</v>
       </c>
       <c r="B23" s="9"/>
-      <c r="C23" s="10" t="s">
-        <v>19</v>
+      <c r="C23" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="D23" s="2">
-        <v>5.56</v>
+        <v>6.09</v>
       </c>
       <c r="E23" s="3">
-        <v>4.8099999999999996</v>
+        <v>5.28</v>
       </c>
       <c r="F23" s="2">
-        <v>4.04</v>
+        <v>4.09</v>
       </c>
       <c r="G23" s="4">
-        <v>5.54</v>
+        <v>5.88</v>
       </c>
       <c r="H23" s="5">
-        <v>4.88</v>
+        <v>5.4</v>
       </c>
       <c r="I23" s="4">
-        <v>4.1500000000000004</v>
+        <v>4.68</v>
       </c>
       <c r="J23" s="6">
-        <v>5.41</v>
+        <v>6.49</v>
       </c>
       <c r="K23" s="7">
-        <v>4.88</v>
+        <v>5.92</v>
       </c>
       <c r="L23" s="6">
-        <v>3.62</v>
-      </c>
-      <c r="M23" s="11">
-        <v>4.71</v>
-      </c>
-      <c r="N23" s="11">
-        <v>7.2</v>
-      </c>
-      <c r="O23" s="11">
-        <v>6.07</v>
-      </c>
-      <c r="S23" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="T23" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="U23" s="30">
-        <v>15</v>
-      </c>
-      <c r="V23" s="30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" ht="23.25">
+        <v>5.18</v>
+      </c>
+      <c r="M23" s="8">
+        <v>3</v>
+      </c>
+      <c r="N23" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O23" s="8">
+        <v>3.07</v>
+      </c>
+      <c r="S23" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="T23" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="U23" s="25">
+        <v>10</v>
+      </c>
+      <c r="V23" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="20">
         <v>21</v>
       </c>
       <c r="B24" s="12"/>
-      <c r="C24" s="12" t="s">
-        <v>20</v>
+      <c r="C24" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="D24" s="2">
-        <v>6.18</v>
+        <v>5.8</v>
       </c>
       <c r="E24" s="3">
-        <v>5.37</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="F24" s="2">
-        <v>4.72</v>
+        <v>3.05</v>
       </c>
       <c r="G24" s="4">
-        <v>6.26</v>
+        <v>5.34</v>
       </c>
       <c r="H24" s="5">
-        <v>5.49</v>
+        <v>4.99</v>
       </c>
       <c r="I24" s="4">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="J24" s="6">
-        <v>5.63</v>
+        <v>6.16</v>
       </c>
       <c r="K24" s="7">
-        <v>5.17</v>
+        <v>5.22</v>
       </c>
       <c r="L24" s="6">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="M24" s="8">
-        <v>3.29</v>
+        <v>5.25</v>
       </c>
       <c r="N24" s="8">
-        <v>3.93</v>
+        <v>6.75</v>
       </c>
       <c r="O24" s="8">
-        <v>3.93</v>
-      </c>
-      <c r="S24" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="T24" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="U24" s="30">
-        <v>6</v>
-      </c>
-      <c r="V24" s="30">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" ht="33.75">
+        <v>6.15</v>
+      </c>
+      <c r="S24" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="T24" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="U24" s="25">
+        <v>8</v>
+      </c>
+      <c r="V24" s="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="22">
         <v>22</v>
       </c>
       <c r="B25" s="9"/>
-      <c r="C25" s="10" t="s">
-        <v>21</v>
+      <c r="C25" s="12" t="s">
+        <v>26</v>
       </c>
       <c r="D25" s="2">
-        <v>6.04</v>
+        <v>6.23</v>
       </c>
       <c r="E25" s="3">
-        <v>5.34</v>
+        <v>5.88</v>
       </c>
       <c r="F25" s="2">
-        <v>4.82</v>
+        <v>5.24</v>
       </c>
       <c r="G25" s="4">
-        <v>5.67</v>
+        <v>6.13</v>
       </c>
       <c r="H25" s="5">
-        <v>5.42</v>
+        <v>5.55</v>
       </c>
       <c r="I25" s="4">
-        <v>4.8600000000000003</v>
+        <v>5.09</v>
       </c>
       <c r="J25" s="6">
-        <v>6.22</v>
+        <v>6.95</v>
       </c>
       <c r="K25" s="7">
-        <v>5.83</v>
+        <v>6.15</v>
       </c>
       <c r="L25" s="6">
-        <v>5.21</v>
-      </c>
-      <c r="M25" s="11">
-        <v>3.3</v>
-      </c>
-      <c r="N25" s="11">
-        <v>3.6</v>
-      </c>
-      <c r="O25" s="11">
-        <v>3.86</v>
-      </c>
-      <c r="S25" s="30" t="s">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="M25" s="8">
+        <v>3.4</v>
+      </c>
+      <c r="N25" s="8">
+        <v>6.1</v>
+      </c>
+      <c r="O25" s="8">
+        <v>4</v>
+      </c>
+      <c r="S25" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="T25" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="U25" s="30">
-        <v>10</v>
-      </c>
-      <c r="V25" s="30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" ht="22.5">
+      <c r="T25" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="U25" s="25">
+        <v>15</v>
+      </c>
+      <c r="V25" s="25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="20">
         <v>23</v>
       </c>
       <c r="B26" s="12"/>
-      <c r="C26" s="1" t="s">
-        <v>22</v>
+      <c r="C26" s="10" t="s">
+        <v>25</v>
       </c>
       <c r="D26" s="2">
-        <v>6.09</v>
+        <v>6.23</v>
       </c>
       <c r="E26" s="3">
-        <v>5.28</v>
+        <v>5.88</v>
       </c>
       <c r="F26" s="2">
-        <v>4.09</v>
+        <v>5.24</v>
       </c>
       <c r="G26" s="4">
-        <v>5.88</v>
+        <v>6.13</v>
       </c>
       <c r="H26" s="5">
-        <v>5.4</v>
+        <v>5.55</v>
       </c>
       <c r="I26" s="4">
-        <v>4.68</v>
+        <v>5.09</v>
       </c>
       <c r="J26" s="6">
-        <v>6.49</v>
+        <v>6.95</v>
       </c>
       <c r="K26" s="7">
-        <v>5.92</v>
+        <v>6.15</v>
       </c>
       <c r="L26" s="6">
-        <v>5.18</v>
-      </c>
-      <c r="M26" s="8">
-        <v>3</v>
-      </c>
-      <c r="N26" s="8">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="O26" s="8">
-        <v>3.07</v>
-      </c>
-      <c r="S26" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="T26" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="U26" s="30">
-        <v>10</v>
-      </c>
-      <c r="V26" s="30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" ht="22.5">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="M26" s="11">
+        <v>3.4</v>
+      </c>
+      <c r="N26" s="11">
+        <v>6.1</v>
+      </c>
+      <c r="O26" s="11">
+        <v>4</v>
+      </c>
+      <c r="S26" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="T26" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="U26" s="25">
+        <v>7</v>
+      </c>
+      <c r="V26" s="25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="22">
         <v>24</v>
       </c>
       <c r="B27" s="9"/>
       <c r="C27" s="10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D27" s="2">
-        <v>5.59</v>
+        <v>6.07</v>
       </c>
       <c r="E27" s="3">
-        <v>5.4</v>
+        <v>5.69</v>
       </c>
       <c r="F27" s="2">
-        <v>4.83</v>
+        <v>5.24</v>
       </c>
       <c r="G27" s="4">
-        <v>5.88</v>
+        <v>6.27</v>
       </c>
       <c r="H27" s="5">
-        <v>5.4</v>
+        <v>5.89</v>
       </c>
       <c r="I27" s="4">
-        <v>4.68</v>
+        <v>5.51</v>
       </c>
       <c r="J27" s="6">
-        <v>6.49</v>
+        <v>6.81</v>
       </c>
       <c r="K27" s="7">
-        <v>5.92</v>
+        <v>6.28</v>
       </c>
       <c r="L27" s="6">
-        <v>5.18</v>
+        <v>5.77</v>
       </c>
       <c r="M27" s="11">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="N27" s="11">
         <v>4.4000000000000004</v>
       </c>
       <c r="O27" s="11">
-        <v>3.07</v>
-      </c>
-      <c r="S27" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="T27" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="U27" s="30">
-        <v>0</v>
-      </c>
-      <c r="V27" s="30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" ht="22.5">
+        <v>3</v>
+      </c>
+      <c r="S27" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="T27" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="U27" s="25">
+        <v>14</v>
+      </c>
+      <c r="V27" s="25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="20">
         <v>25</v>
       </c>
       <c r="B28" s="12"/>
       <c r="C28" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D28" s="2">
-        <v>5.8</v>
+        <v>5.64</v>
       </c>
       <c r="E28" s="3">
-        <v>4.9800000000000004</v>
+        <v>5.41</v>
       </c>
       <c r="F28" s="2">
-        <v>3.05</v>
+        <v>5.17</v>
       </c>
       <c r="G28" s="4">
-        <v>5.34</v>
+        <v>5.94</v>
       </c>
       <c r="H28" s="5">
-        <v>4.99</v>
+        <v>5.55</v>
       </c>
       <c r="I28" s="4">
-        <v>4.04</v>
+        <v>4.76</v>
       </c>
       <c r="J28" s="6">
-        <v>6.16</v>
+        <v>6.31</v>
       </c>
       <c r="K28" s="7">
-        <v>5.22</v>
+        <v>5.51</v>
       </c>
       <c r="L28" s="6">
-        <v>3.2</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="M28" s="8">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="N28" s="8">
-        <v>6.75</v>
+        <v>3.88</v>
       </c>
       <c r="O28" s="8">
-        <v>6.15</v>
-      </c>
-      <c r="S28" s="30" t="s">
+        <v>3.81</v>
+      </c>
+      <c r="S28" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="T28" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="U28" s="30">
-        <v>8</v>
-      </c>
-      <c r="V28" s="30">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" ht="33.75">
+      <c r="T28" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="U28" s="25">
+        <v>12</v>
+      </c>
+      <c r="V28" s="25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="22">
         <v>26</v>
       </c>
       <c r="B29" s="9"/>
-      <c r="C29" s="10" t="s">
-        <v>25</v>
+      <c r="C29" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="D29" s="2">
-        <v>6.23</v>
+        <v>5.51</v>
       </c>
       <c r="E29" s="3">
-        <v>5.88</v>
+        <v>5.16</v>
       </c>
       <c r="F29" s="2">
-        <v>5.24</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="G29" s="4">
-        <v>6.13</v>
+        <v>5.63</v>
       </c>
       <c r="H29" s="5">
-        <v>5.55</v>
+        <v>5.29</v>
       </c>
       <c r="I29" s="4">
-        <v>5.09</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="J29" s="6">
-        <v>6.95</v>
+        <v>7.43</v>
       </c>
       <c r="K29" s="7">
-        <v>6.15</v>
+        <v>6.26</v>
       </c>
       <c r="L29" s="6">
-        <v>4.5599999999999996</v>
+        <v>5.03</v>
       </c>
       <c r="M29" s="11">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N29" s="11">
-        <v>6.1</v>
+        <v>5.38</v>
       </c>
       <c r="O29" s="11">
-        <v>4</v>
-      </c>
-      <c r="S29" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="T29" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="U29" s="30">
-        <v>7</v>
-      </c>
-      <c r="V29" s="30">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" ht="23.25">
+        <v>2.85</v>
+      </c>
+      <c r="S29" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="T29" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="U29" s="25">
+        <v>17</v>
+      </c>
+      <c r="V29" s="25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="20">
         <v>27</v>
       </c>
       <c r="B30" s="12"/>
-      <c r="C30" s="12" t="s">
-        <v>26</v>
+      <c r="C30" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="D30" s="2">
-        <v>6.23</v>
+        <v>5.59</v>
       </c>
       <c r="E30" s="3">
+        <v>5.4</v>
+      </c>
+      <c r="F30" s="2">
+        <v>4.83</v>
+      </c>
+      <c r="G30" s="4">
         <v>5.88</v>
       </c>
-      <c r="F30" s="2">
-        <v>5.24</v>
-      </c>
-      <c r="G30" s="4">
-        <v>6.13</v>
-      </c>
       <c r="H30" s="5">
-        <v>5.55</v>
+        <v>5.4</v>
       </c>
       <c r="I30" s="4">
-        <v>5.09</v>
+        <v>4.68</v>
       </c>
       <c r="J30" s="6">
-        <v>6.95</v>
+        <v>6.49</v>
       </c>
       <c r="K30" s="7">
-        <v>6.15</v>
+        <v>5.92</v>
       </c>
       <c r="L30" s="6">
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="M30" s="8">
-        <v>3.4</v>
-      </c>
-      <c r="N30" s="8">
-        <v>6.1</v>
-      </c>
-      <c r="O30" s="8">
-        <v>4</v>
-      </c>
-      <c r="S30" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="T30" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="U30" s="30">
-        <v>15</v>
-      </c>
-      <c r="V30" s="30">
+        <v>5.18</v>
+      </c>
+      <c r="M30" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="N30" s="11">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O30" s="11">
+        <v>3.07</v>
+      </c>
+      <c r="S30" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="T30" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="U30" s="25">
+        <v>0</v>
+      </c>
+      <c r="V30" s="25">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="33.75">
+    <row r="31" spans="1:22">
       <c r="A31" s="22">
         <v>28</v>
       </c>
       <c r="B31" s="9"/>
       <c r="C31" s="10" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D31" s="2">
+        <v>5.56</v>
+      </c>
+      <c r="E31" s="3">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="F31" s="2">
+        <v>4.04</v>
+      </c>
+      <c r="G31" s="4">
+        <v>5.54</v>
+      </c>
+      <c r="H31" s="5">
+        <v>4.88</v>
+      </c>
+      <c r="I31" s="4">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="J31" s="6">
+        <v>5.41</v>
+      </c>
+      <c r="K31" s="7">
+        <v>4.88</v>
+      </c>
+      <c r="L31" s="6">
+        <v>3.62</v>
+      </c>
+      <c r="M31" s="11">
+        <v>4.71</v>
+      </c>
+      <c r="N31" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="O31" s="11">
         <v>6.07</v>
       </c>
-      <c r="E31" s="3">
-        <v>5.69</v>
-      </c>
-      <c r="F31" s="2">
-        <v>5.24</v>
-      </c>
-      <c r="G31" s="4">
-        <v>6.27</v>
-      </c>
-      <c r="H31" s="5">
-        <v>5.89</v>
-      </c>
-      <c r="I31" s="4">
-        <v>5.51</v>
-      </c>
-      <c r="J31" s="6">
-        <v>6.81</v>
-      </c>
-      <c r="K31" s="7">
-        <v>6.28</v>
-      </c>
-      <c r="L31" s="6">
-        <v>5.77</v>
-      </c>
-      <c r="M31" s="11">
-        <v>3.17</v>
-      </c>
-      <c r="N31" s="11">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="O31" s="11">
-        <v>3</v>
-      </c>
-      <c r="S31" s="30" t="s">
-        <v>61</v>
-      </c>
-      <c r="T31" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="U31" s="30">
-        <v>14</v>
-      </c>
-      <c r="V31" s="30">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" ht="22.5">
+      <c r="S31" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="T31" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="U31" s="25">
+        <v>15</v>
+      </c>
+      <c r="V31" s="25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="20">
         <v>29</v>
       </c>
       <c r="B32" s="12"/>
-      <c r="C32" s="1" t="s">
-        <v>28</v>
+      <c r="C32" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="D32" s="2">
-        <v>5.64</v>
+        <v>6.04</v>
       </c>
       <c r="E32" s="3">
-        <v>5.41</v>
+        <v>5.34</v>
       </c>
       <c r="F32" s="2">
-        <v>5.17</v>
+        <v>4.82</v>
       </c>
       <c r="G32" s="4">
-        <v>5.94</v>
+        <v>5.67</v>
       </c>
       <c r="H32" s="5">
-        <v>5.55</v>
+        <v>5.42</v>
       </c>
       <c r="I32" s="4">
-        <v>4.76</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="J32" s="6">
-        <v>6.31</v>
+        <v>6.22</v>
       </c>
       <c r="K32" s="7">
-        <v>5.51</v>
+        <v>5.83</v>
       </c>
       <c r="L32" s="6">
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="M32" s="8">
-        <v>3</v>
-      </c>
-      <c r="N32" s="8">
-        <v>3.88</v>
-      </c>
-      <c r="O32" s="8">
-        <v>3.81</v>
-      </c>
-      <c r="S32" s="30" t="s">
+        <v>5.21</v>
+      </c>
+      <c r="M32" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="N32" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="O32" s="11">
+        <v>3.86</v>
+      </c>
+      <c r="S32" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="T32" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="U32" s="30">
-        <v>12</v>
-      </c>
-      <c r="V32" s="30">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" ht="23.25">
+      <c r="T32" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="U32" s="25">
+        <v>10</v>
+      </c>
+      <c r="V32" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="22">
         <v>30</v>
       </c>
       <c r="B33" s="9"/>
-      <c r="C33" s="9" t="s">
-        <v>29</v>
+      <c r="C33" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="2">
-        <v>5.51</v>
+        <v>6.18</v>
       </c>
       <c r="E33" s="3">
-        <v>5.16</v>
+        <v>5.37</v>
       </c>
       <c r="F33" s="2">
-        <v>4.5999999999999996</v>
+        <v>4.72</v>
       </c>
       <c r="G33" s="4">
+        <v>6.26</v>
+      </c>
+      <c r="H33" s="5">
+        <v>5.49</v>
+      </c>
+      <c r="I33" s="4">
+        <v>3.96</v>
+      </c>
+      <c r="J33" s="6">
         <v>5.63</v>
       </c>
-      <c r="H33" s="5">
-        <v>5.29</v>
-      </c>
-      <c r="I33" s="4">
-        <v>4.8099999999999996</v>
-      </c>
-      <c r="J33" s="6">
-        <v>7.43</v>
-      </c>
       <c r="K33" s="7">
-        <v>6.26</v>
+        <v>5.17</v>
       </c>
       <c r="L33" s="6">
-        <v>5.03</v>
-      </c>
-      <c r="M33" s="11">
-        <v>4</v>
-      </c>
-      <c r="N33" s="11">
-        <v>5.38</v>
-      </c>
-      <c r="O33" s="11">
-        <v>2.85</v>
-      </c>
-      <c r="S33" s="30" t="s">
+        <v>4.5</v>
+      </c>
+      <c r="M33" s="8">
+        <v>3.29</v>
+      </c>
+      <c r="N33" s="8">
+        <v>3.93</v>
+      </c>
+      <c r="O33" s="8">
+        <v>3.93</v>
+      </c>
+      <c r="S33" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="T33" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="U33" s="30">
-        <v>17</v>
-      </c>
-      <c r="V33" s="30">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" ht="22.5">
+      <c r="T33" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="U33" s="25">
+        <v>6</v>
+      </c>
+      <c r="V33" s="25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22">
       <c r="A34" s="20">
         <v>31</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="D34" s="2">
+        <v>6.61</v>
+      </c>
+      <c r="E34" s="3">
+        <v>6.15</v>
+      </c>
+      <c r="F34" s="2">
+        <v>5.28</v>
+      </c>
       <c r="G34" s="4">
-        <v>6.52</v>
+        <v>6.75</v>
       </c>
       <c r="H34" s="5">
-        <v>5.71</v>
+        <v>6.03</v>
       </c>
       <c r="I34" s="4">
-        <v>4.3899999999999997</v>
+        <v>4.28</v>
       </c>
       <c r="J34" s="6">
+        <v>6.7</v>
+      </c>
+      <c r="K34" s="7">
+        <v>6.05</v>
+      </c>
+      <c r="L34" s="6">
+        <v>4.7</v>
+      </c>
+      <c r="M34" s="8">
+        <v>4.75</v>
+      </c>
+      <c r="N34" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="O34" s="8">
+        <v>3.75</v>
+      </c>
+      <c r="S34" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="T34" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="U34" s="25">
+        <v>8</v>
+      </c>
+      <c r="V34" s="25">
         <v>0</v>
       </c>
-      <c r="K34" s="7">
-        <v>0</v>
-      </c>
-      <c r="L34" s="6">
-        <v>0</v>
-      </c>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8">
-        <v>3.73</v>
-      </c>
-      <c r="O34" s="8">
-        <v>0</v>
-      </c>
-      <c r="S34" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="T34" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="U34" s="30">
-        <v>10</v>
-      </c>
-      <c r="V34" s="30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:22" ht="22.5">
+    </row>
+    <row r="35" spans="1:22">
       <c r="A35" s="22">
         <v>32</v>
       </c>
@@ -3180,16 +3182,16 @@
       <c r="O35" s="11">
         <v>0</v>
       </c>
-      <c r="S35" s="30" t="s">
+      <c r="S35" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="T35" s="30" t="s">
+      <c r="T35" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="U35" s="30">
+      <c r="U35" s="25">
         <v>5</v>
       </c>
-      <c r="V35" s="30">
+      <c r="V35" s="25">
         <v>0</v>
       </c>
     </row>

--- a/윈윈대진_입결.xlsx
+++ b/윈윈대진_입결.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\대진대_입학상담_2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09687E2C-DB56-49B3-95D4-AAFBCA7D1F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36EFC52-4D79-4245-B12A-BD787D5998AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{333CE5E8-D45C-448F-B07C-A850148192AA}"/>
   </bookViews>
@@ -1263,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7DC7B2B-FDA9-4AF7-939D-6B0F2B1CC895}">
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="3.625" bestFit="1" customWidth="1"/>
@@ -1379,7 +1379,7 @@
       <c r="U3" s="27"/>
       <c r="V3" s="27"/>
     </row>
-    <row r="4" spans="1:22" ht="22.5">
+    <row r="4" spans="1:22">
       <c r="A4" s="20">
         <v>1</v>
       </c>
@@ -1483,16 +1483,16 @@
         <v>5.9</v>
       </c>
       <c r="S5" s="25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="T5" s="25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U5" s="25">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="V5" s="25">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -1540,16 +1540,16 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="S6" s="25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T6" s="25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="U6" s="25">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="V6" s="25">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -1603,10 +1603,10 @@
         <v>60</v>
       </c>
       <c r="U7" s="25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V7" s="25">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1660,13 +1660,13 @@
         <v>60</v>
       </c>
       <c r="U8" s="25">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V8" s="25">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="22.5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" s="22">
         <v>6</v>
       </c>
@@ -1768,16 +1768,16 @@
         <v>3.5</v>
       </c>
       <c r="S10" s="25" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="T10" s="25" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="U10" s="25">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="V10" s="25">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1825,16 +1825,16 @@
         <v>3.7</v>
       </c>
       <c r="S11" s="25" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="T11" s="25" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="U11" s="25">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="V11" s="25">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1939,19 +1939,19 @@
         <v>7.25</v>
       </c>
       <c r="S13" s="25" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="T13" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U13" s="25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="V13" s="25">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" ht="22.5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" s="20">
         <v>11</v>
       </c>
@@ -2056,13 +2056,13 @@
         <v>59</v>
       </c>
       <c r="T15" s="25" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="U15" s="25">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V15" s="25">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -2110,19 +2110,19 @@
         <v>3.5</v>
       </c>
       <c r="S16" s="25" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="T16" s="25" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="U16" s="25">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V16" s="25">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" ht="22.5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="22">
         <v>14</v>
       </c>
@@ -2179,7 +2179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="22.5">
+    <row r="18" spans="1:22">
       <c r="A18" s="20">
         <v>15</v>
       </c>
@@ -2283,16 +2283,16 @@
         <v>8.9</v>
       </c>
       <c r="S19" s="25" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="T19" s="25" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="U19" s="25">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="V19" s="25">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -2340,16 +2340,16 @@
         <v>7.75</v>
       </c>
       <c r="S20" s="25" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="T20" s="25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="U20" s="25">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="V20" s="25">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -2448,16 +2448,16 @@
         <v>0</v>
       </c>
       <c r="S22" s="25" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="T22" s="25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U22" s="25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V22" s="25">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -2505,16 +2505,16 @@
         <v>3.07</v>
       </c>
       <c r="S23" s="25" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="T23" s="25" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="U23" s="25">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="V23" s="25">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -2562,16 +2562,16 @@
         <v>6.15</v>
       </c>
       <c r="S24" s="25" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="T24" s="25" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="U24" s="25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V24" s="25">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -2622,13 +2622,13 @@
         <v>55</v>
       </c>
       <c r="T25" s="25" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="U25" s="25">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V25" s="25">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -2676,16 +2676,16 @@
         <v>4</v>
       </c>
       <c r="S26" s="25" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="T26" s="25" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="U26" s="25">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V26" s="25">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -2733,16 +2733,16 @@
         <v>3</v>
       </c>
       <c r="S27" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T27" s="25" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="U27" s="25">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="V27" s="25">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -2793,13 +2793,13 @@
         <v>55</v>
       </c>
       <c r="T28" s="25" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="U28" s="25">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="V28" s="25">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -2847,16 +2847,16 @@
         <v>2.85</v>
       </c>
       <c r="S29" s="25" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="T29" s="25" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="U29" s="25">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="V29" s="25">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -2904,13 +2904,13 @@
         <v>3.07</v>
       </c>
       <c r="S30" s="25" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="T30" s="25" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="U30" s="25">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V30" s="25">
         <v>5</v>
@@ -2961,16 +2961,16 @@
         <v>6.07</v>
       </c>
       <c r="S31" s="25" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="T31" s="25" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="U31" s="25">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V31" s="25">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -3021,13 +3021,13 @@
         <v>55</v>
       </c>
       <c r="T32" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U32" s="25">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V32" s="25">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:22">
@@ -3078,13 +3078,13 @@
         <v>59</v>
       </c>
       <c r="T33" s="25" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="U33" s="25">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="V33" s="25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -3132,16 +3132,16 @@
         <v>3.75</v>
       </c>
       <c r="S34" s="25" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="T34" s="25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U34" s="25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V34" s="25">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:22">
@@ -3194,6 +3194,12 @@
       <c r="V35" s="25">
         <v>0</v>
       </c>
+    </row>
+    <row r="39" spans="1:22">
+      <c r="S39" s="25"/>
+      <c r="T39" s="25"/>
+      <c r="U39" s="25"/>
+      <c r="V39" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/윈윈대진_입결.xlsx
+++ b/윈윈대진_입결.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\대진대_입학상담_2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36EFC52-4D79-4245-B12A-BD787D5998AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25EF5882-C534-4F85-B41D-B0EB52C4CBDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{333CE5E8-D45C-448F-B07C-A850148192AA}"/>
   </bookViews>
@@ -1263,6 +1263,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7DC7B2B-FDA9-4AF7-939D-6B0F2B1CC895}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:V39"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -1828,13 +1831,13 @@
         <v>55</v>
       </c>
       <c r="T11" s="25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="U11" s="25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V11" s="25">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1885,13 +1888,13 @@
         <v>55</v>
       </c>
       <c r="T12" s="25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="U12" s="25">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V12" s="25">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3215,5 +3218,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="59" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>